--- a/Daily_Report/Top 7 broker List with its Turnover 2024-12-24.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-12-24.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
   <si>
     <t>Date: 2024-12-24</t>
   </si>
@@ -59,106 +59,109 @@
     <t>7</t>
   </si>
   <si>
-    <t>Deevyaa Securities &amp; Stock House Pvt. Ltd</t>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Sumeru Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Stock Broker Opal Securities Investment Pvt. Limited</t>
-  </si>
-  <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>59</t>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>45</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>38</t>
   </si>
   <si>
-    <t>554,790,791.54</t>
-  </si>
-  <si>
-    <t>434,570,856.5</t>
-  </si>
-  <si>
-    <t>406,629,881.77</t>
-  </si>
-  <si>
-    <t>371,876,374.5</t>
-  </si>
-  <si>
-    <t>319,206,204.6</t>
-  </si>
-  <si>
-    <t>268,566,961.29</t>
-  </si>
-  <si>
-    <t>222,284,152.6</t>
-  </si>
-  <si>
-    <t>164,029,865.9</t>
-  </si>
-  <si>
-    <t>267,075,393.4</t>
-  </si>
-  <si>
-    <t>250,843,267.37</t>
-  </si>
-  <si>
-    <t>160,281,688.0</t>
-  </si>
-  <si>
-    <t>141,959,392.1</t>
-  </si>
-  <si>
-    <t>45,759,959.3</t>
-  </si>
-  <si>
-    <t>111,782,434.2</t>
-  </si>
-  <si>
-    <t>390,760,925.65</t>
-  </si>
-  <si>
-    <t>167,495,463.1</t>
-  </si>
-  <si>
-    <t>155,786,614.4</t>
-  </si>
-  <si>
-    <t>211,594,686.5</t>
-  </si>
-  <si>
-    <t>177,246,812.5</t>
-  </si>
-  <si>
-    <t>222,807,001.99</t>
-  </si>
-  <si>
-    <t>110,501,718.4</t>
+    <t>42</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>539,731,690.77</t>
+  </si>
+  <si>
+    <t>410,075,771.2</t>
+  </si>
+  <si>
+    <t>375,748,459.91</t>
+  </si>
+  <si>
+    <t>331,995,531.1</t>
+  </si>
+  <si>
+    <t>317,287,312.89</t>
+  </si>
+  <si>
+    <t>317,285,423.24</t>
+  </si>
+  <si>
+    <t>284,063,132.25</t>
+  </si>
+  <si>
+    <t>317,862,525.97</t>
+  </si>
+  <si>
+    <t>233,865,626.3</t>
+  </si>
+  <si>
+    <t>191,381,924.51</t>
+  </si>
+  <si>
+    <t>186,283,370.4</t>
+  </si>
+  <si>
+    <t>181,802,527.7</t>
+  </si>
+  <si>
+    <t>166,179,589.84</t>
+  </si>
+  <si>
+    <t>130,136,224.65</t>
+  </si>
+  <si>
+    <t>221,869,164.8</t>
+  </si>
+  <si>
+    <t>176,210,144.9</t>
+  </si>
+  <si>
+    <t>184,366,535.4</t>
+  </si>
+  <si>
+    <t>145,712,160.69</t>
+  </si>
+  <si>
+    <t>135,484,785.19</t>
+  </si>
+  <si>
+    <t>151,105,833.4</t>
+  </si>
+  <si>
+    <t>153,926,907.6</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -176,352 +179,340 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>TVCL</t>
-  </si>
-  <si>
-    <t>115,484,270.0</t>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>12,945,802.6</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>11,146,575.2</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>8,892,680.5</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>8,557,234.1</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>7,842,221.6</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>11,646,731.0</t>
+  </si>
+  <si>
+    <t>SMHL</t>
+  </si>
+  <si>
+    <t>10,859,792.0</t>
+  </si>
+  <si>
+    <t>9,182,331.8</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>8,885,090.6</t>
+  </si>
+  <si>
+    <t>JOSHI</t>
+  </si>
+  <si>
+    <t>6,008,579.0</t>
+  </si>
+  <si>
+    <t>9,001,053.0</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>6,280,826.9</t>
+  </si>
+  <si>
+    <t>6,107,744.5</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>5,121,328.0</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>4,702,621.7</t>
   </si>
   <si>
     <t>PRVU</t>
   </si>
   <si>
-    <t>14,004,239.4</t>
-  </si>
-  <si>
-    <t>NESDO</t>
-  </si>
-  <si>
-    <t>8,099,680.0</t>
+    <t>37,061,228.29</t>
+  </si>
+  <si>
+    <t>8,250,447.5</t>
+  </si>
+  <si>
+    <t>5,114,697.9</t>
+  </si>
+  <si>
+    <t>5,002,310.0</t>
+  </si>
+  <si>
+    <t>4,837,471.4</t>
+  </si>
+  <si>
+    <t>8,409,483.1</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>8,362,365.1</t>
+  </si>
+  <si>
+    <t>7,888,836.6</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>4,702,051.9</t>
+  </si>
+  <si>
+    <t>DOLTI</t>
+  </si>
+  <si>
+    <t>4,695,095.8</t>
+  </si>
+  <si>
+    <t>9,064,232.0</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>5,287,277.0</t>
+  </si>
+  <si>
+    <t>4,902,194.0</t>
   </si>
   <si>
     <t>NFS</t>
   </si>
   <si>
-    <t>4,983,076.4</t>
+    <t>4,660,399.09</t>
+  </si>
+  <si>
+    <t>DLBS</t>
+  </si>
+  <si>
+    <t>4,095,600.5</t>
+  </si>
+  <si>
+    <t>8,505,382.6</t>
+  </si>
+  <si>
+    <t>4,453,048.4</t>
+  </si>
+  <si>
+    <t>SAPDBL</t>
+  </si>
+  <si>
+    <t>3,564,146.0</t>
+  </si>
+  <si>
+    <t>3,412,726.0</t>
+  </si>
+  <si>
+    <t>KBSH</t>
+  </si>
+  <si>
+    <t>3,231,931.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>12,185,118.6</t>
+  </si>
+  <si>
+    <t>RHGCL</t>
+  </si>
+  <si>
+    <t>8,828,301.6</t>
+  </si>
+  <si>
+    <t>7,688,805.0</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>7,045,416.1</t>
+  </si>
+  <si>
+    <t>5,928,341.5</t>
+  </si>
+  <si>
+    <t>MHCL</t>
+  </si>
+  <si>
+    <t>9,855,427.0</t>
+  </si>
+  <si>
+    <t>7,843,980.1</t>
+  </si>
+  <si>
+    <t>5,519,491.5</t>
+  </si>
+  <si>
+    <t>5,366,038.5</t>
+  </si>
+  <si>
+    <t>UMRH</t>
+  </si>
+  <si>
+    <t>4,970,512.59</t>
+  </si>
+  <si>
+    <t>CKHL</t>
+  </si>
+  <si>
+    <t>11,455,754.0</t>
+  </si>
+  <si>
+    <t>7,015,521.1</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>6,218,778.6</t>
+  </si>
+  <si>
+    <t>SIFC</t>
+  </si>
+  <si>
+    <t>5,932,125.5</t>
+  </si>
+  <si>
+    <t>5,569,269.3</t>
+  </si>
+  <si>
+    <t>6,556,741.0</t>
+  </si>
+  <si>
+    <t>PPL</t>
+  </si>
+  <si>
+    <t>6,230,740.5</t>
+  </si>
+  <si>
+    <t>NYADI</t>
+  </si>
+  <si>
+    <t>5,611,850.9</t>
+  </si>
+  <si>
+    <t>MLBBL</t>
+  </si>
+  <si>
+    <t>4,767,750.0</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>3,680,791.6</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>9,430,652.5</t>
+  </si>
+  <si>
+    <t>4,098,149.5</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>4,082,021.5</t>
+  </si>
+  <si>
+    <t>3,673,862.0</t>
+  </si>
+  <si>
+    <t>3,521,029.0</t>
+  </si>
+  <si>
+    <t>4,873,764.2</t>
+  </si>
+  <si>
+    <t>RAWA</t>
+  </si>
+  <si>
+    <t>4,710,546.5</t>
   </si>
   <si>
     <t>HDL</t>
   </si>
   <si>
-    <t>3,021,094.9</t>
-  </si>
-  <si>
-    <t>CKHL</t>
-  </si>
-  <si>
-    <t>70,771,138.0</t>
-  </si>
-  <si>
-    <t>ULHC</t>
-  </si>
-  <si>
-    <t>35,406,708.0</t>
-  </si>
-  <si>
-    <t>CIT</t>
-  </si>
-  <si>
-    <t>23,757,810.8</t>
-  </si>
-  <si>
-    <t>15,004,686.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>14,030,000.0</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>63,961,648.3</t>
-  </si>
-  <si>
-    <t>23,772,585.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>13,373,987.0</t>
-  </si>
-  <si>
-    <t>12,710,157.0</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>12,451,050.0</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>33,797,459.0</t>
-  </si>
-  <si>
-    <t>19,139,648.0</t>
-  </si>
-  <si>
-    <t>MHCL</t>
-  </si>
-  <si>
-    <t>13,649,995.1</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>10,491,489.0</t>
-  </si>
-  <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>8,839,599.0</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>40,793,166.0</t>
-  </si>
-  <si>
-    <t>36,782,778.0</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>21,528,000.0</t>
+    <t>4,141,850.6</t>
+  </si>
+  <si>
+    <t>NHDL</t>
+  </si>
+  <si>
+    <t>3,477,594.0</t>
+  </si>
+  <si>
+    <t>3,195,467.8</t>
+  </si>
+  <si>
+    <t>HHL</t>
+  </si>
+  <si>
+    <t>13,237,708.7</t>
+  </si>
+  <si>
+    <t>11,627,442.7</t>
+  </si>
+  <si>
+    <t>SPC</t>
+  </si>
+  <si>
+    <t>5,411,324.2</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>4,899,002.0</t>
   </si>
   <si>
     <t>MBL</t>
   </si>
   <si>
-    <t>6,307,598.0</t>
-  </si>
-  <si>
-    <t>5,668,117.5</t>
-  </si>
-  <si>
-    <t>RHGCL</t>
-  </si>
-  <si>
-    <t>18,600,525.6</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>5,568,080.0</t>
-  </si>
-  <si>
-    <t>3,879,882.2</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>2,436,550.0</t>
-  </si>
-  <si>
-    <t>2,341,920.0</t>
-  </si>
-  <si>
-    <t>14,749,992.1</t>
-  </si>
-  <si>
-    <t>BEDC</t>
-  </si>
-  <si>
-    <t>13,928,800.0</t>
-  </si>
-  <si>
-    <t>12,994,477.5</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>6,292,800.0</t>
-  </si>
-  <si>
-    <t>3,875,349.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>257,286,125.0</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>93,352,383.0</t>
-  </si>
-  <si>
-    <t>NSIF2</t>
-  </si>
-  <si>
-    <t>14,272,304.25</t>
-  </si>
-  <si>
-    <t>SMHL</t>
-  </si>
-  <si>
-    <t>5,557,576.0</t>
-  </si>
-  <si>
-    <t>NMB50</t>
-  </si>
-  <si>
-    <t>3,424,454.9</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>50,558,313.1</t>
-  </si>
-  <si>
-    <t>UHEWA</t>
-  </si>
-  <si>
-    <t>33,593,150.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>15,640,332.0</t>
-  </si>
-  <si>
-    <t>TSHL</t>
-  </si>
-  <si>
-    <t>14,655,741.0</t>
-  </si>
-  <si>
-    <t>SIFC</t>
-  </si>
-  <si>
-    <t>5,164,839.0</t>
-  </si>
-  <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>42,688,438.0</t>
-  </si>
-  <si>
-    <t>12,011,556.6</t>
-  </si>
-  <si>
-    <t>11,258,656.5</t>
-  </si>
-  <si>
-    <t>6,337,256.0</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>4,745,587.3</t>
-  </si>
-  <si>
-    <t>66,010,718.2</t>
-  </si>
-  <si>
-    <t>VLBS</t>
-  </si>
-  <si>
-    <t>39,647,400.0</t>
-  </si>
-  <si>
-    <t>25,875,881.0</t>
-  </si>
-  <si>
-    <t>10,056,276.5</t>
-  </si>
-  <si>
-    <t>SSHL</t>
-  </si>
-  <si>
-    <t>7,112,980.0</t>
-  </si>
-  <si>
-    <t>82,332,552.0</t>
-  </si>
-  <si>
-    <t>MKHL</t>
-  </si>
-  <si>
-    <t>23,699,326.8</t>
-  </si>
-  <si>
-    <t>17,361,301.0</t>
-  </si>
-  <si>
-    <t>16,440,841.1</t>
-  </si>
-  <si>
-    <t>6,658,847.2</t>
-  </si>
-  <si>
-    <t>197,714,220.0</t>
-  </si>
-  <si>
-    <t>5,605,376.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>4,868,529.6</t>
-  </si>
-  <si>
-    <t>WNLB</t>
-  </si>
-  <si>
-    <t>2,476,640.0</t>
-  </si>
-  <si>
-    <t>EDBL</t>
-  </si>
-  <si>
-    <t>1,518,920.0</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>33,681,200.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>11,824,966.0</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>3,850,327.0</t>
-  </si>
-  <si>
-    <t>MLBBL</t>
-  </si>
-  <si>
-    <t>3,735,750.0</t>
-  </si>
-  <si>
-    <t>3,420,349.0</t>
+    <t>4,355,221.3</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -539,109 +530,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>284,384,425.2</t>
-  </si>
-  <si>
-    <t>258,085,993.8</t>
-  </si>
-  <si>
-    <t>201,509,946.6</t>
-  </si>
-  <si>
-    <t>199,687,229.2</t>
-  </si>
-  <si>
-    <t>177,821,976.1</t>
+    <t>200,742,653.7</t>
+  </si>
+  <si>
+    <t>192,720,466.9</t>
+  </si>
+  <si>
+    <t>95,217,961.3</t>
+  </si>
+  <si>
+    <t>86,306,627.3</t>
+  </si>
+  <si>
+    <t>85,914,118.0</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,336,346,423.8</t>
+    <t>1,587,685,207.2</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,026,206,279.0</t>
+    <t>1,164,716,288.45</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>729,498,832.2</t>
+    <t>742,070,805.9</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>514,045,409.4</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>453,411,075.7</t>
+    <t>367,267,629.9</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>291,415,601.0</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>340,928,308.6</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>250,168,726.7</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>179,126,078.7</t>
+    <t>192,732,722.3</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>94,569,778.2</t>
+    <t>90,180,280.0</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>62,100,512.4</t>
+    <t>71,174,799.7</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>63,184,206.21</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>44,190,491.9</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>22,129,279.6</t>
+    <t>32,879,953.4</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>20,348,281.26</t>
+    <t>27,653,609.11</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>14,334,379.0</t>
+    <t>25,335,191.0</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>24,508,859.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>12,426,692.0</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>4,069,980.0</t>
+    <t>7,412,476.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -653,214 +644,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>121,747,317.3</t>
-  </si>
-  <si>
-    <t>15,309,476.9</t>
-  </si>
-  <si>
-    <t>9,424,630.6</t>
-  </si>
-  <si>
-    <t>6,300,954.4</t>
-  </si>
-  <si>
-    <t>5,389,672.6</t>
-  </si>
-  <si>
-    <t>137,731,342.8</t>
-  </si>
-  <si>
-    <t>34,577,434.7</t>
-  </si>
-  <si>
-    <t>25,358,761.0</t>
-  </si>
-  <si>
-    <t>23,249,438.4</t>
-  </si>
-  <si>
-    <t>22,180,896.6</t>
-  </si>
-  <si>
-    <t>107,004,484.8</t>
-  </si>
-  <si>
-    <t>46,762,059.1</t>
-  </si>
-  <si>
-    <t>25,925,590.9</t>
-  </si>
-  <si>
-    <t>12,996,617.0</t>
-  </si>
-  <si>
-    <t>11,107,889.6</t>
-  </si>
-  <si>
-    <t>42,205,485.7</t>
-  </si>
-  <si>
-    <t>35,513,267.4</t>
-  </si>
-  <si>
-    <t>30,086,293.0</t>
-  </si>
-  <si>
-    <t>27,236,559.2</t>
-  </si>
-  <si>
-    <t>8,512,190.0</t>
-  </si>
-  <si>
-    <t>43,566,452.9</t>
-  </si>
-  <si>
-    <t>41,960,404.0</t>
-  </si>
-  <si>
-    <t>31,534,825.6</t>
-  </si>
-  <si>
-    <t>8,603,813.6</t>
-  </si>
-  <si>
-    <t>7,132,127.8</t>
-  </si>
-  <si>
-    <t>29,804,860.8</t>
-  </si>
-  <si>
-    <t>4,023,882.2</t>
-  </si>
-  <si>
-    <t>2,733,015.7</t>
-  </si>
-  <si>
-    <t>2,559,193.79</t>
-  </si>
-  <si>
-    <t>2,450,010.0</t>
-  </si>
-  <si>
-    <t>28,941,735.0</t>
-  </si>
-  <si>
-    <t>26,002,617.5</t>
-  </si>
-  <si>
-    <t>21,902,270.3</t>
-  </si>
-  <si>
-    <t>20,171,358.7</t>
-  </si>
-  <si>
-    <t>5,445,861.0</t>
-  </si>
-  <si>
-    <t>257,307,675.0</t>
-  </si>
-  <si>
-    <t>94,742,287.5</t>
-  </si>
-  <si>
-    <t>18,053,866.85</t>
-  </si>
-  <si>
-    <t>8,445,128.8</t>
-  </si>
-  <si>
-    <t>5,721,160.4</t>
-  </si>
-  <si>
-    <t>100,653,512.4</t>
-  </si>
-  <si>
-    <t>29,051,032.4</t>
-  </si>
-  <si>
-    <t>24,658,174.5</t>
-  </si>
-  <si>
-    <t>5,822,842.0</t>
-  </si>
-  <si>
-    <t>2,216,641.0</t>
-  </si>
-  <si>
-    <t>71,085,216.5</t>
-  </si>
-  <si>
-    <t>32,994,568.6</t>
-  </si>
-  <si>
-    <t>16,828,775.8</t>
-  </si>
-  <si>
-    <t>12,428,307.9</t>
-  </si>
-  <si>
-    <t>10,397,838.5</t>
-  </si>
-  <si>
-    <t>71,704,032.3</t>
-  </si>
-  <si>
-    <t>55,489,135.6</t>
-  </si>
-  <si>
-    <t>43,275,223.7</t>
-  </si>
-  <si>
-    <t>29,588,516.7</t>
-  </si>
-  <si>
-    <t>4,262,288.09</t>
-  </si>
-  <si>
-    <t>82,727,893.0</t>
-  </si>
-  <si>
-    <t>51,977,628.1</t>
-  </si>
-  <si>
-    <t>24,336,452.4</t>
-  </si>
-  <si>
-    <t>7,108,340.5</t>
-  </si>
-  <si>
-    <t>3,516,058.4</t>
-  </si>
-  <si>
-    <t>198,896,604.5</t>
-  </si>
-  <si>
-    <t>7,000,383.7</t>
-  </si>
-  <si>
-    <t>6,906,586.6</t>
-  </si>
-  <si>
-    <t>4,567,937.2</t>
-  </si>
-  <si>
-    <t>2,763,664.7</t>
-  </si>
-  <si>
-    <t>33,786,200.0</t>
-  </si>
-  <si>
-    <t>22,328,006.3</t>
-  </si>
-  <si>
-    <t>15,802,578.2</t>
-  </si>
-  <si>
-    <t>12,721,444.7</t>
-  </si>
-  <si>
-    <t>11,592,746.7</t>
+    <t>83,756,288.09</t>
+  </si>
+  <si>
+    <t>58,668,495.0</t>
+  </si>
+  <si>
+    <t>41,254,533.79</t>
+  </si>
+  <si>
+    <t>32,619,026.9</t>
+  </si>
+  <si>
+    <t>27,883,670.6</t>
+  </si>
+  <si>
+    <t>67,776,922.59</t>
+  </si>
+  <si>
+    <t>56,182,231.7</t>
+  </si>
+  <si>
+    <t>27,600,563.2</t>
+  </si>
+  <si>
+    <t>19,094,935.2</t>
+  </si>
+  <si>
+    <t>17,907,138.39</t>
+  </si>
+  <si>
+    <t>63,930,819.7</t>
+  </si>
+  <si>
+    <t>43,454,008.7</t>
+  </si>
+  <si>
+    <t>27,743,756.8</t>
+  </si>
+  <si>
+    <t>16,391,594.1</t>
+  </si>
+  <si>
+    <t>10,967,472.7</t>
+  </si>
+  <si>
+    <t>50,200,000.2</t>
+  </si>
+  <si>
+    <t>44,805,994.8</t>
+  </si>
+  <si>
+    <t>34,119,015.1</t>
+  </si>
+  <si>
+    <t>21,704,502.0</t>
+  </si>
+  <si>
+    <t>13,874,312.0</t>
+  </si>
+  <si>
+    <t>53,972,447.5</t>
+  </si>
+  <si>
+    <t>42,059,738.1</t>
+  </si>
+  <si>
+    <t>31,950,869.7</t>
+  </si>
+  <si>
+    <t>15,580,809.7</t>
+  </si>
+  <si>
+    <t>11,706,586.7</t>
+  </si>
+  <si>
+    <t>48,379,801.1</t>
+  </si>
+  <si>
+    <t>37,768,545.6</t>
+  </si>
+  <si>
+    <t>30,036,122.6</t>
+  </si>
+  <si>
+    <t>17,079,850.89</t>
+  </si>
+  <si>
+    <t>13,010,929.6</t>
+  </si>
+  <si>
+    <t>36,468,942.5</t>
+  </si>
+  <si>
+    <t>29,106,308.3</t>
+  </si>
+  <si>
+    <t>27,634,390.55</t>
+  </si>
+  <si>
+    <t>11,902,181.5</t>
+  </si>
+  <si>
+    <t>7,079,213.1</t>
+  </si>
+  <si>
+    <t>62,569,052.5</t>
+  </si>
+  <si>
+    <t>61,711,004.3</t>
+  </si>
+  <si>
+    <t>24,864,338.4</t>
+  </si>
+  <si>
+    <t>20,451,430.39</t>
+  </si>
+  <si>
+    <t>18,873,102.5</t>
+  </si>
+  <si>
+    <t>51,776,718.6</t>
+  </si>
+  <si>
+    <t>51,564,752.7</t>
+  </si>
+  <si>
+    <t>22,984,354.0</t>
+  </si>
+  <si>
+    <t>19,653,476.6</t>
+  </si>
+  <si>
+    <t>10,458,364.5</t>
+  </si>
+  <si>
+    <t>56,570,584.2</t>
+  </si>
+  <si>
+    <t>45,381,706.1</t>
+  </si>
+  <si>
+    <t>25,165,588.8</t>
+  </si>
+  <si>
+    <t>17,527,845.5</t>
+  </si>
+  <si>
+    <t>14,854,220.6</t>
+  </si>
+  <si>
+    <t>50,714,198.6</t>
+  </si>
+  <si>
+    <t>26,104,700.3</t>
+  </si>
+  <si>
+    <t>18,147,617.3</t>
+  </si>
+  <si>
+    <t>16,729,087.9</t>
+  </si>
+  <si>
+    <t>15,055,455.6</t>
+  </si>
+  <si>
+    <t>39,087,747.2</t>
+  </si>
+  <si>
+    <t>37,458,419.9</t>
+  </si>
+  <si>
+    <t>13,474,711.2</t>
+  </si>
+  <si>
+    <t>10,661,560.19</t>
+  </si>
+  <si>
+    <t>10,633,757.0</t>
+  </si>
+  <si>
+    <t>41,788,968.9</t>
+  </si>
+  <si>
+    <t>38,457,231.2</t>
+  </si>
+  <si>
+    <t>17,434,957.0</t>
+  </si>
+  <si>
+    <t>15,589,073.3</t>
+  </si>
+  <si>
+    <t>14,831,087.5</t>
+  </si>
+  <si>
+    <t>49,921,294.8</t>
+  </si>
+  <si>
+    <t>32,846,251.1</t>
+  </si>
+  <si>
+    <t>18,851,093.8</t>
+  </si>
+  <si>
+    <t>14,264,587.2</t>
+  </si>
+  <si>
+    <t>12,667,154.2</t>
   </si>
 </sst>
 </file>
@@ -1462,12 +1453,12 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1477,37 +1468,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1517,37 +1508,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1557,1070 +1548,1070 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="V8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2081582314611869</v>
+        <v>0.02398562623130591</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1628529316714546</v>
+        <v>0.02840141217297063</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1572969699658676</v>
+        <v>0.02395499638815805</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0908835874433857</v>
+        <v>0.1116317083462091</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1277956550096458</v>
+        <v>0.02650431567256026</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S9" s="16">
-        <v>0.0692584281773307</v>
+        <v>0.02856806942922072</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.06635647178385491</v>
+        <v>0.02994187430319022</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.02065206729680429</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.02648240340613423</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0.01671550936364289</v>
+      </c>
+      <c r="K10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="10">
-        <v>0.02524237895310828</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.08147510922652035</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="14">
-        <v>0.05846246443208118</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>67</v>
-      </c>
       <c r="L10" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.05146777077660254</v>
+        <v>0.02485107999093786</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1152320270406172</v>
+        <v>0.02635581304391954</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02073255762007239</v>
+        <v>0.01666410308424606</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V10" s="18">
-        <v>0.06266213689585354</v>
+        <v>0.01567626310647358</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01459952133915335</v>
+        <v>0.01647611332088615</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.05466959057343046</v>
+        <v>0.02239179304139293</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.03288982831705581</v>
+        <v>0.01625487567257878</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L11" s="15" t="s">
         <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03670573350714432</v>
+        <v>0.01540592393835388</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06744229808119462</v>
+        <v>0.02486338494879037</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01444661019069288</v>
+        <v>0.01545042299750373</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05845885704404462</v>
+        <v>0.01254702069842434</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.008981901783333593</v>
+        <v>0.01585460747689644</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03452759377572297</v>
+        <v>0.0216669484617432</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0312573117958635</v>
+        <v>0.01362967129985488</v>
       </c>
       <c r="K12" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="M12" s="16">
-        <v>0.02821230311849241</v>
+        <v>0.01506740161057547</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01976026126404436</v>
+        <v>0.01481953960599097</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S12" s="16">
-        <v>0.009072411543869228</v>
+        <v>0.01468834922326323</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02830971046021389</v>
+        <v>0.01201397017968705</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.005445466914761736</v>
+        <v>0.0145298520248311</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.03228472363056403</v>
+        <v>0.01465236286069076</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03062010579695327</v>
+        <v>0.01251534524220374</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02377026239401503</v>
+        <v>0.01457089312007308</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01775691517996264</v>
+        <v>0.0147976159433761</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S13" s="16">
-        <v>0.008720059938362942</v>
+        <v>0.01290825294833044</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01743421181704161</v>
+        <v>0.01137750955007995</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D16" s="10">
-        <v>0.4637534164566471</v>
+        <v>0.02257625188288701</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1163407815866732</v>
+        <v>0.0240331853090471</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I16" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.03048782689021242</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="14">
-        <v>0.1049810648794022</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>139</v>
-      </c>
       <c r="M16" s="16">
-        <v>0.177507157556738</v>
+        <v>0.01974948571830339</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2579290465333267</v>
+        <v>0.02972275321633259</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="S16" s="16">
-        <v>0.7361822133406252</v>
+        <v>0.01536081976357736</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1515231725070804</v>
+        <v>0.04660129104099886</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1682659200942896</v>
+        <v>0.01635683386944583</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0773018933449809</v>
+        <v>0.0191281237539254</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="I17" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.01867079136313791</v>
+      </c>
+      <c r="K17" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="J17" s="14">
-        <v>0.02953928655640226</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="L17" s="15" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1066144630814669</v>
+        <v>0.01876754328395838</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="P17" s="18">
-        <v>0.0742445681145134</v>
+        <v>0.01291620979907136</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02087142801507358</v>
+        <v>0.01484640060642453</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="V17" s="18">
-        <v>0.05319752155826874</v>
+        <v>0.04093260046772577</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02572556081928718</v>
+        <v>0.01424560597698253</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03599029195368972</v>
+        <v>0.01345968693504709</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J18" s="14">
-        <v>0.0276877253855342</v>
+        <v>0.01655037681721845</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M18" s="16">
-        <v>0.06958194382418344</v>
+        <v>0.01690339289027858</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05438898351539122</v>
+        <v>0.01286537889804166</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01812780535786626</v>
+        <v>0.01305402106943638</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="V18" s="18">
-        <v>0.01732164418814263</v>
+        <v>0.01904972376083486</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D19" s="10">
-        <v>0.0100174265410444</v>
+        <v>0.01305355275683139</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03372462920784933</v>
+        <v>0.01308548048156423</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01558482611365121</v>
+        <v>0.01578749118870873</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02704198811640291</v>
+        <v>0.01436088607639695</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P19" s="18">
-        <v>0.05150539326327368</v>
+        <v>0.01157897542899201</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0092216853034037</v>
+        <v>0.01096045940115405</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01680619133799644</v>
+        <v>0.01724617327562401</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D20" s="10">
-        <v>0.006172515752167769</v>
+        <v>0.01098386772794909</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01188491801221373</v>
+        <v>0.01212096141514249</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01167053262131931</v>
+        <v>0.01482180206762248</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01912727047950716</v>
+        <v>0.01108687092204055</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02086064463673022</v>
+        <v>0.01109728897704059</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="S20" s="16">
-        <v>0.00565564726445747</v>
+        <v>0.01007127200288333</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01538728226908246</v>
+        <v>0.01533187804240302</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2568779036915703</v>
+        <v>0.3051912591556354</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1972615131898605</v>
+        <v>0.2238864662964366</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1402272101182575</v>
+        <v>0.142643845649139</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D34" s="22">
-        <v>0.0871565071466732</v>
+        <v>0.09881188351854292</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D35" s="22">
-        <v>0.06553461562253388</v>
+        <v>0.07059766628043374</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D36" s="22">
-        <v>0.0480884424423042</v>
+        <v>0.05601708311160376</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03443233788294531</v>
+        <v>0.0370478618384084</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01817858449272019</v>
+        <v>0.01733481743068278</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01193721115975524</v>
+        <v>0.01368150729255792</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D40" s="22">
-        <v>0.008494474726165923</v>
+        <v>0.01214552315820003</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D41" s="22">
-        <v>0.004253779448661425</v>
+        <v>0.006320317361160972</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D42" s="22">
-        <v>0.003911428758818268</v>
+        <v>0.005315688365808092</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002755412191525833</v>
+        <v>0.004870032678502191</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D44" s="22">
-        <v>0.002388708896083781</v>
+        <v>0.004711191806006219</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0007823479839110092</v>
+        <v>0.001424856056882034</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2798,12 +2789,12 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -2813,37 +2804,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -2853,37 +2844,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -2893,835 +2884,835 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="V8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2194472567936046</v>
+        <v>0.1551813420118251</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G9" s="12">
-        <v>0.3169364460131486</v>
+        <v>0.1652790224637392</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J9" s="14">
-        <v>0.263149585402394</v>
+        <v>0.1701425994275874</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M9" s="16">
-        <v>0.11349332357224</v>
+        <v>0.1512068552057688</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1364837282990582</v>
+        <v>0.1701059112849261</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1109773914696335</v>
+        <v>0.1524803774657013</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V9" s="18">
-        <v>0.13020152206748</v>
+        <v>0.1283832302035739</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02759504507496904</v>
+        <v>0.1086993704525697</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G10" s="12">
-        <v>0.07956685125754631</v>
+        <v>0.1370045139111598</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1149990721204542</v>
+        <v>0.1156465384060608</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="M10" s="16">
-        <v>0.09549750894433333</v>
+        <v>0.1349596322924721</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1314523445826529</v>
+        <v>0.1325604157177758</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0149827893219716</v>
+        <v>0.1190364978457622</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1169791782088563</v>
+        <v>0.1024642236021813</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01698771995416332</v>
+        <v>0.07643526312332123</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G11" s="12">
-        <v>0.05835357024223276</v>
+        <v>0.0673060081536463</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06375722017071082</v>
+        <v>0.07383598273867907</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08090401827879495</v>
+        <v>0.1027695011042876</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P11" s="18">
-        <v>0.09879139297908246</v>
+        <v>0.1007001175306055</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01017629155414658</v>
+        <v>0.09466593924575027</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="V11" s="18">
-        <v>0.09853275658122647</v>
+        <v>0.09728256648835147</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D12" s="10">
-        <v>0.0113573521694477</v>
+        <v>0.06043563396002292</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G12" s="12">
-        <v>0.05349976431288829</v>
+        <v>0.04656440721704359</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0319617853548481</v>
+        <v>0.04362384906095463</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M12" s="16">
-        <v>0.07324089688843624</v>
+        <v>0.06537588601896695</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02695377933139336</v>
+        <v>0.0491063117449976</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="S12" s="16">
-        <v>0.009529071586513126</v>
+        <v>0.05383118683987103</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="V12" s="18">
-        <v>0.09074582449563252</v>
+        <v>0.04189977560877226</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D13" s="10">
-        <v>0.009714783810564133</v>
+        <v>0.05166209632830748</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G13" s="12">
-        <v>0.05104092064213239</v>
+        <v>0.04366787715255292</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0273169535688056</v>
+        <v>0.02918833706631013</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02288983808515644</v>
+        <v>0.04179065891046869</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02234332446306089</v>
+        <v>0.03689585503120821</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="S13" s="16">
-        <v>0.009122529398779031</v>
+        <v>0.04100701969582232</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02449954680215021</v>
+        <v>0.02492126677589995</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D16" s="10">
-        <v>0.4637922599276063</v>
+        <v>0.1159262158772571</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2316158824147933</v>
+        <v>0.1262613454301052</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1748155255845353</v>
+        <v>0.1505544007114491</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1928168531717252</v>
+        <v>0.1527556664150531</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2591675594265688</v>
+        <v>0.1231935397691724</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S16" s="16">
-        <v>0.7405847820492879</v>
+        <v>0.1317078120805762</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1519955408643018</v>
+        <v>0.175740140596862</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1707711968962294</v>
+        <v>0.1143364478227338</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12">
-        <v>0.06684993244594165</v>
+        <v>0.1257444509562383</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08114152471131611</v>
+        <v>0.1207768253018786</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1492139307709638</v>
+        <v>0.07862967375948512</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P17" s="18">
-        <v>0.162834015601713</v>
+        <v>0.1180583602843453</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02606569202002585</v>
+        <v>0.1212070532812039</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1004480348186549</v>
+        <v>0.1156301095458332</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03254175650529505</v>
+        <v>0.04606796085019145</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05674143613447764</v>
+        <v>0.05604904169963797</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J18" s="14">
-        <v>0.04138597912860417</v>
+        <v>0.06697456273281256</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M18" s="16">
-        <v>0.1163699193265099</v>
+        <v>0.05466223367486768</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07624053683573041</v>
+        <v>0.04246848409046487</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02571644168950874</v>
+        <v>0.05495038764138845</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07109178956376937</v>
+        <v>0.06636233871915985</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01522218632433608</v>
+        <v>0.03789184654105316</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01339906234600433</v>
+        <v>0.04792645159817235</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03056417754126039</v>
+        <v>0.04664781727701107</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="M19" s="16">
-        <v>0.07956546510862039</v>
+        <v>0.05038949724585615</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02226880429504032</v>
+        <v>0.03360222664610679</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01700855971966497</v>
+        <v>0.04913264889641074</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05723055175639182</v>
+        <v>0.05021625681239738</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01031228435500157</v>
+        <v>0.03496756411148468</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G20" s="12">
-        <v>0.005100758522678338</v>
+        <v>0.02550349285303008</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02557076832312407</v>
+        <v>0.03953235258384802</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0114615726953098</v>
+        <v>0.04534836824494834</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0110150064420145</v>
+        <v>0.03351459881205985</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01029041206938659</v>
+        <v>0.04674367750194914</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="V20" s="18">
-        <v>0.05215282585106788</v>
+        <v>0.04459274281624063</v>
       </c>
     </row>
   </sheetData>
